--- a/ig/main/CodeSystem-TRE-R344-NiveauExpertise.xlsx
+++ b/ig/main/CodeSystem-TRE-R344-NiveauExpertise.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -457,7 +457,7 @@
     <t>52</t>
   </si>
   <si>
-    <t>Autorisation par l’ARS pour la sous-traitance de préparation pharmaceutique</t>
+    <t>Autorisation par l'ARS pour la sous-traitance de préparation pharmaceutique présentant un risque pour la santé</t>
   </si>
   <si>
     <t>53</t>
